--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepFinanciallInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepFinanciallInfo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\华夏\需求文档\需求确认材料\数据补录模板\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\code\huaxia\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -5998,27 +5998,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6026,6 +6005,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6052,40 +6043,28 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6098,6 +6077,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6105,6 +6093,18 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6581,7 +6581,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1">
       <formula1>"01 利率,02 汇率,03 股票,04 农产品,05 商品,06 贵金属,99 其他"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1 K1:K1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K1048576"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写" sqref="C2:C65506"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3:D65506">
       <formula1>"01 银行间债券市场,02 商业银行柜台市场,03 上海证券交易所,04 深圳证券交易所,05 全国中小企业股份转让系统,06 上海期货交易所,07 郑州商品交易所,08 大连商品交易所,09 中国金融期货交易所,10 上海黄金交易所,11 区域性产权/资产交易市场,12 区域性商品交易所,13 区域性贵金属交易所,14 艺术品市场,15 基金市场,16 信托市场,17 全国银行间同业拆借市场,18 上海票据交易所,99 其他交易流通场所"</formula1>
@@ -6594,8 +6594,8 @@
       <formula1>0</formula1>
       <formula2>9999999999999.99</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I65520">
-      <formula1>"01 是,02 否"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576">
+      <formula1>"01 对冲,02 无风险套利,03 投机,99 其他"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
@@ -6676,13 +6676,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="80"/>
+      <c r="B1" s="98"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="88" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="29" t="s">
@@ -6690,25 +6690,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="92"/>
+      <c r="A3" s="89"/>
       <c r="B3" s="26" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="92"/>
+      <c r="A4" s="89"/>
       <c r="B4" s="26" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="93"/>
+      <c r="A5" s="90"/>
       <c r="B5" s="24" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="17" customFormat="1">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="91" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="29" t="s">
@@ -6716,13 +6716,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="17" customFormat="1">
-      <c r="A7" s="95"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="23" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="17" customFormat="1">
-      <c r="A8" s="96" t="s">
+      <c r="A8" s="93" t="s">
         <v>38</v>
       </c>
       <c r="B8" s="22" t="s">
@@ -6730,13 +6730,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="17" customFormat="1">
-      <c r="A9" s="95"/>
+      <c r="A9" s="92"/>
       <c r="B9" s="23" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="94" t="s">
         <v>41</v>
       </c>
       <c r="B10" s="26" t="s">
@@ -6744,61 +6744,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="97"/>
+      <c r="A11" s="95"/>
       <c r="B11" s="26" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="97"/>
+      <c r="A12" s="95"/>
       <c r="B12" s="26" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="97"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="97"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="26" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="97"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="26" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="97"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="26" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="97"/>
+      <c r="A17" s="95"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="97"/>
+      <c r="A18" s="95"/>
       <c r="B18" s="26" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="97"/>
+      <c r="A19" s="95"/>
       <c r="B19" s="26" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="97"/>
+      <c r="A20" s="95"/>
       <c r="B20" s="26" t="s">
         <v>52</v>
       </c>
@@ -6812,7 +6812,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="94" t="s">
         <v>55</v>
       </c>
       <c r="B22" s="29" t="s">
@@ -6820,19 +6820,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="97"/>
+      <c r="A23" s="95"/>
       <c r="B23" s="26" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="85"/>
+      <c r="A24" s="96"/>
       <c r="B24" s="24" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="84" t="s">
+      <c r="A25" s="94" t="s">
         <v>59</v>
       </c>
       <c r="B25" s="26" t="s">
@@ -6840,67 +6840,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="97"/>
+      <c r="A26" s="95"/>
       <c r="B26" s="26" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="97"/>
+      <c r="A27" s="95"/>
       <c r="B27" s="21" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="97"/>
+      <c r="A28" s="95"/>
       <c r="B28" s="21" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="97"/>
+      <c r="A29" s="95"/>
       <c r="B29" s="21" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="97"/>
+      <c r="A30" s="95"/>
       <c r="B30" s="21" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="97"/>
+      <c r="A31" s="95"/>
       <c r="B31" s="21" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="97"/>
+      <c r="A32" s="95"/>
       <c r="B32" s="21" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="97"/>
+      <c r="A33" s="95"/>
       <c r="B33" s="21" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="97"/>
+      <c r="A34" s="95"/>
       <c r="B34" s="21" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="85"/>
+      <c r="A35" s="96"/>
       <c r="B35" s="41" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="84" t="s">
+      <c r="A36" s="94" t="s">
         <v>71</v>
       </c>
       <c r="B36" s="21" t="s">
@@ -6908,25 +6908,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="97"/>
+      <c r="A37" s="95"/>
       <c r="B37" s="26" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="97"/>
+      <c r="A38" s="95"/>
       <c r="B38" s="21" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="85"/>
+      <c r="A39" s="96"/>
       <c r="B39" s="21" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="84" t="s">
+      <c r="A40" s="94" t="s">
         <v>76</v>
       </c>
       <c r="B40" s="20" t="s">
@@ -6934,43 +6934,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="97"/>
+      <c r="A41" s="95"/>
       <c r="B41" s="21" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="97"/>
+      <c r="A42" s="95"/>
       <c r="B42" s="21" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="97"/>
+      <c r="A43" s="95"/>
       <c r="B43" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="97"/>
+      <c r="A44" s="95"/>
       <c r="B44" s="21" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="97"/>
+      <c r="A45" s="95"/>
       <c r="B45" s="21" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="85"/>
+      <c r="A46" s="96"/>
       <c r="B46" s="24" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="84" t="s">
+      <c r="A47" s="94" t="s">
         <v>84</v>
       </c>
       <c r="B47" s="29" t="s">
@@ -6978,61 +6978,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="97"/>
+      <c r="A48" s="95"/>
       <c r="B48" s="21" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="97"/>
+      <c r="A49" s="95"/>
       <c r="B49" s="21" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="97"/>
+      <c r="A50" s="95"/>
       <c r="B50" s="21" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="97"/>
+      <c r="A51" s="95"/>
       <c r="B51" s="21" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="97"/>
+      <c r="A52" s="95"/>
       <c r="B52" s="21" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="97"/>
+      <c r="A53" s="95"/>
       <c r="B53" s="26" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="97"/>
+      <c r="A54" s="95"/>
       <c r="B54" s="21" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="97"/>
+      <c r="A55" s="95"/>
       <c r="B55" s="26" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="85"/>
+      <c r="A56" s="96"/>
       <c r="B56" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="84" t="s">
+      <c r="A57" s="94" t="s">
         <v>95</v>
       </c>
       <c r="B57" s="20" t="s">
@@ -7040,19 +7040,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="97"/>
+      <c r="A58" s="95"/>
       <c r="B58" s="21" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="85"/>
+      <c r="A59" s="96"/>
       <c r="B59" s="24" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="94" t="s">
         <v>99</v>
       </c>
       <c r="B60" s="34" t="s">
@@ -7060,37 +7060,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="97"/>
+      <c r="A61" s="95"/>
       <c r="B61" s="21" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="97"/>
+      <c r="A62" s="95"/>
       <c r="B62" s="35" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="97"/>
+      <c r="A63" s="95"/>
       <c r="B63" s="21" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="97"/>
+      <c r="A64" s="95"/>
       <c r="B64" s="21" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="85"/>
+      <c r="A65" s="96"/>
       <c r="B65" s="28" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="84" t="s">
+      <c r="A66" s="94" t="s">
         <v>106</v>
       </c>
       <c r="B66" s="34" t="s">
@@ -7098,37 +7098,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="97"/>
+      <c r="A67" s="95"/>
       <c r="B67" s="21" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="97"/>
+      <c r="A68" s="95"/>
       <c r="B68" s="21" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="97"/>
+      <c r="A69" s="95"/>
       <c r="B69" s="21" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="97"/>
+      <c r="A70" s="95"/>
       <c r="B70" s="21" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="85"/>
+      <c r="A71" s="96"/>
       <c r="B71" s="28" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="17" customFormat="1">
-      <c r="A72" s="84" t="s">
+      <c r="A72" s="94" t="s">
         <v>113</v>
       </c>
       <c r="B72" s="21" t="s">
@@ -7136,103 +7136,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="17" customFormat="1">
-      <c r="A73" s="97"/>
+      <c r="A73" s="95"/>
       <c r="B73" s="21" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="17" customFormat="1">
-      <c r="A74" s="97"/>
+      <c r="A74" s="95"/>
       <c r="B74" s="21" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="17" customFormat="1">
-      <c r="A75" s="97"/>
+      <c r="A75" s="95"/>
       <c r="B75" s="21" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="17" customFormat="1">
-      <c r="A76" s="97"/>
+      <c r="A76" s="95"/>
       <c r="B76" s="21" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="17" customFormat="1">
-      <c r="A77" s="97"/>
+      <c r="A77" s="95"/>
       <c r="B77" s="36" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="17" customFormat="1">
-      <c r="A78" s="97"/>
+      <c r="A78" s="95"/>
       <c r="B78" s="21" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="17" customFormat="1">
-      <c r="A79" s="97"/>
+      <c r="A79" s="95"/>
       <c r="B79" s="21" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="17" customFormat="1">
-      <c r="A80" s="97"/>
+      <c r="A80" s="95"/>
       <c r="B80" s="21" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="17" customFormat="1">
-      <c r="A81" s="97"/>
+      <c r="A81" s="95"/>
       <c r="B81" s="36" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="17" customFormat="1">
-      <c r="A82" s="97"/>
+      <c r="A82" s="95"/>
       <c r="B82" s="21" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="17" customFormat="1">
-      <c r="A83" s="97"/>
+      <c r="A83" s="95"/>
       <c r="B83" s="21" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="17" customFormat="1">
-      <c r="A84" s="97"/>
+      <c r="A84" s="95"/>
       <c r="B84" s="21" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="17" customFormat="1">
-      <c r="A85" s="97"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="36" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="17" customFormat="1">
-      <c r="A86" s="97"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="36" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="17" customFormat="1">
-      <c r="A87" s="97"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="36" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="17" customFormat="1">
-      <c r="A88" s="85"/>
+      <c r="A88" s="96"/>
       <c r="B88" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="17" customFormat="1">
-      <c r="A89" s="84" t="s">
+      <c r="A89" s="94" t="s">
         <v>131</v>
       </c>
       <c r="B89" s="26" t="s">
@@ -7240,38 +7240,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="17" customFormat="1">
-      <c r="A90" s="97"/>
+      <c r="A90" s="95"/>
       <c r="B90" s="26" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="17" customFormat="1">
-      <c r="A91" s="97"/>
+      <c r="A91" s="95"/>
       <c r="B91" s="26" t="s">
         <v>134</v>
       </c>
       <c r="F91" s="42"/>
     </row>
     <row r="92" spans="1:6" s="17" customFormat="1">
-      <c r="A92" s="97"/>
+      <c r="A92" s="95"/>
       <c r="B92" s="43" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="17" customFormat="1">
-      <c r="A93" s="97"/>
+      <c r="A93" s="95"/>
       <c r="B93" s="26" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="17" customFormat="1">
-      <c r="A94" s="85"/>
+      <c r="A94" s="96"/>
       <c r="B94" s="24" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="17" customFormat="1">
-      <c r="A95" s="84" t="s">
+      <c r="A95" s="94" t="s">
         <v>138</v>
       </c>
       <c r="B95" s="37" t="s">
@@ -7279,43 +7279,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="17" customFormat="1">
-      <c r="A96" s="97"/>
+      <c r="A96" s="95"/>
       <c r="B96" s="36" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="17" customFormat="1">
-      <c r="A97" s="97"/>
+      <c r="A97" s="95"/>
       <c r="B97" s="36" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="17" customFormat="1">
-      <c r="A98" s="97"/>
+      <c r="A98" s="95"/>
       <c r="B98" s="36" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="17" customFormat="1">
-      <c r="A99" s="97"/>
+      <c r="A99" s="95"/>
       <c r="B99" s="36" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="17" customFormat="1">
-      <c r="A100" s="97"/>
+      <c r="A100" s="95"/>
       <c r="B100" s="36" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="17" customFormat="1">
-      <c r="A101" s="85"/>
+      <c r="A101" s="96"/>
       <c r="B101" s="32" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="17" customFormat="1">
-      <c r="A102" s="84" t="s">
+      <c r="A102" s="94" t="s">
         <v>146</v>
       </c>
       <c r="B102" s="20" t="s">
@@ -7323,7 +7323,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="17" customFormat="1">
-      <c r="A103" s="85"/>
+      <c r="A103" s="96"/>
       <c r="B103" s="24" t="s">
         <v>148</v>
       </c>
@@ -7341,10 +7341,10 @@
       <c r="B105" s="27"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="79" t="s">
+      <c r="A107" s="97" t="s">
         <v>151</v>
       </c>
-      <c r="B107" s="80"/>
+      <c r="B107" s="98"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="47"/>
@@ -7515,17 +7515,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="98" t="s">
+      <c r="A137" s="82" t="s">
         <v>180</v>
       </c>
-      <c r="B137" s="99"/>
+      <c r="B137" s="83"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="100"/>
-      <c r="B138" s="101"/>
+      <c r="A138" s="84"/>
+      <c r="B138" s="85"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="86" t="s">
+      <c r="A139" s="79" t="s">
         <v>181</v>
       </c>
       <c r="B139" s="49" t="s">
@@ -7533,31 +7533,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="87"/>
+      <c r="A140" s="80"/>
       <c r="B140" s="50" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="87"/>
+      <c r="A141" s="80"/>
       <c r="B141" s="50" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="87"/>
+      <c r="A142" s="80"/>
       <c r="B142" s="50" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="88"/>
+      <c r="A143" s="81"/>
       <c r="B143" s="52" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="86" t="s">
+      <c r="A144" s="79" t="s">
         <v>187</v>
       </c>
       <c r="B144" s="49" t="s">
@@ -7565,43 +7565,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="87"/>
+      <c r="A145" s="80"/>
       <c r="B145" s="50" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="87"/>
+      <c r="A146" s="80"/>
       <c r="B146" s="50" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="87"/>
+      <c r="A147" s="80"/>
       <c r="B147" s="50" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="87"/>
+      <c r="A148" s="80"/>
       <c r="B148" s="50" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="87"/>
+      <c r="A149" s="80"/>
       <c r="B149" s="50" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="88"/>
+      <c r="A150" s="81"/>
       <c r="B150" s="52" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="86" t="s">
+      <c r="A151" s="79" t="s">
         <v>195</v>
       </c>
       <c r="B151" s="49" t="s">
@@ -7609,187 +7609,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="87"/>
+      <c r="A152" s="80"/>
       <c r="B152" s="50" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="87"/>
+      <c r="A153" s="80"/>
       <c r="B153" s="50" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="87"/>
+      <c r="A154" s="80"/>
       <c r="B154" s="50" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="87"/>
+      <c r="A155" s="80"/>
       <c r="B155" s="50" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="87"/>
+      <c r="A156" s="80"/>
       <c r="B156" s="50" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="87"/>
+      <c r="A157" s="80"/>
       <c r="B157" s="50" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="87"/>
+      <c r="A158" s="80"/>
       <c r="B158" s="50" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="87"/>
+      <c r="A159" s="80"/>
       <c r="B159" s="50" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="87"/>
+      <c r="A160" s="80"/>
       <c r="B160" s="50" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="87"/>
+      <c r="A161" s="80"/>
       <c r="B161" s="50" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="87"/>
+      <c r="A162" s="80"/>
       <c r="B162" s="50" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="87"/>
+      <c r="A163" s="80"/>
       <c r="B163" s="50" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="87"/>
+      <c r="A164" s="80"/>
       <c r="B164" s="50" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="87"/>
+      <c r="A165" s="80"/>
       <c r="B165" s="50" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="87"/>
+      <c r="A166" s="80"/>
       <c r="B166" s="50" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="87"/>
+      <c r="A167" s="80"/>
       <c r="B167" s="50" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="87"/>
+      <c r="A168" s="80"/>
       <c r="B168" s="50" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="87"/>
+      <c r="A169" s="80"/>
       <c r="B169" s="50" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="87"/>
+      <c r="A170" s="80"/>
       <c r="B170" s="50" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="87"/>
+      <c r="A171" s="80"/>
       <c r="B171" s="50" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="87"/>
+      <c r="A172" s="80"/>
       <c r="B172" s="50" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="87"/>
+      <c r="A173" s="80"/>
       <c r="B173" s="50" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="87"/>
+      <c r="A174" s="80"/>
       <c r="B174" s="50" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="87"/>
+      <c r="A175" s="80"/>
       <c r="B175" s="50" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="87"/>
+      <c r="A176" s="80"/>
       <c r="B176" s="50" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="87"/>
+      <c r="A177" s="80"/>
       <c r="B177" s="50" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="87"/>
+      <c r="A178" s="80"/>
       <c r="B178" s="50" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="87"/>
+      <c r="A179" s="80"/>
       <c r="B179" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="87"/>
+      <c r="A180" s="80"/>
       <c r="B180" s="50" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="88"/>
+      <c r="A181" s="81"/>
       <c r="B181" s="52" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="86" t="s">
+      <c r="A182" s="79" t="s">
         <v>227</v>
       </c>
       <c r="B182" s="49" t="s">
@@ -7797,19 +7797,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="87"/>
+      <c r="A183" s="80"/>
       <c r="B183" s="50" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="88"/>
+      <c r="A184" s="81"/>
       <c r="B184" s="52" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="86" t="s">
+      <c r="A185" s="79" t="s">
         <v>231</v>
       </c>
       <c r="B185" s="49" t="s">
@@ -7817,25 +7817,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="87"/>
+      <c r="A186" s="80"/>
       <c r="B186" s="50" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="87"/>
+      <c r="A187" s="80"/>
       <c r="B187" s="50" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="88"/>
+      <c r="A188" s="81"/>
       <c r="B188" s="52" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="86" t="s">
+      <c r="A189" s="79" t="s">
         <v>236</v>
       </c>
       <c r="B189" s="49" t="s">
@@ -7843,13 +7843,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="88"/>
+      <c r="A190" s="81"/>
       <c r="B190" s="52" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="86" t="s">
+      <c r="A191" s="79" t="s">
         <v>239</v>
       </c>
       <c r="B191" s="49" t="s">
@@ -7857,49 +7857,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="87"/>
+      <c r="A192" s="80"/>
       <c r="B192" s="50" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="87"/>
+      <c r="A193" s="80"/>
       <c r="B193" s="50" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="87"/>
+      <c r="A194" s="80"/>
       <c r="B194" s="50" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="87"/>
+      <c r="A195" s="80"/>
       <c r="B195" s="50" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="87"/>
+      <c r="A196" s="80"/>
       <c r="B196" s="50" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="87"/>
+      <c r="A197" s="80"/>
       <c r="B197" s="50" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="88"/>
+      <c r="A198" s="81"/>
       <c r="B198" s="52" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="86" t="s">
+      <c r="A199" s="79" t="s">
         <v>248</v>
       </c>
       <c r="B199" s="49" t="s">
@@ -7907,13 +7907,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="88"/>
+      <c r="A200" s="81"/>
       <c r="B200" s="52" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="86" t="s">
+      <c r="A201" s="79" t="s">
         <v>251</v>
       </c>
       <c r="B201" s="49" t="s">
@@ -7921,19 +7921,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="87"/>
+      <c r="A202" s="80"/>
       <c r="B202" s="50" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="88"/>
+      <c r="A203" s="81"/>
       <c r="B203" s="52" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="86" t="s">
+      <c r="A204" s="79" t="s">
         <v>255</v>
       </c>
       <c r="B204" s="49" t="s">
@@ -7941,19 +7941,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="87"/>
+      <c r="A205" s="80"/>
       <c r="B205" s="50" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="87"/>
+      <c r="A206" s="80"/>
       <c r="B206" s="50" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="88"/>
+      <c r="A207" s="81"/>
       <c r="B207" s="52" t="s">
         <v>259</v>
       </c>
@@ -7967,7 +7967,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="86" t="s">
+      <c r="A209" s="79" t="s">
         <v>262</v>
       </c>
       <c r="B209" s="49" t="s">
@@ -7975,13 +7975,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="88"/>
+      <c r="A210" s="81"/>
       <c r="B210" s="52" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="86" t="s">
+      <c r="A211" s="79" t="s">
         <v>265</v>
       </c>
       <c r="B211" s="49" t="s">
@@ -7989,19 +7989,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="87"/>
+      <c r="A212" s="80"/>
       <c r="B212" s="50" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="88"/>
+      <c r="A213" s="81"/>
       <c r="B213" s="52" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="86" t="s">
+      <c r="A214" s="79" t="s">
         <v>269</v>
       </c>
       <c r="B214" s="49" t="s">
@@ -8009,19 +8009,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="87"/>
+      <c r="A215" s="80"/>
       <c r="B215" s="50" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="88"/>
+      <c r="A216" s="81"/>
       <c r="B216" s="52" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="86" t="s">
+      <c r="A217" s="79" t="s">
         <v>273</v>
       </c>
       <c r="B217" s="49" t="s">
@@ -8029,13 +8029,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="87"/>
+      <c r="A218" s="80"/>
       <c r="B218" s="50" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="88"/>
+      <c r="A219" s="81"/>
       <c r="B219" s="52" t="s">
         <v>276</v>
       </c>
@@ -8049,7 +8049,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="86" t="s">
+      <c r="A221" s="79" t="s">
         <v>279</v>
       </c>
       <c r="B221" s="49" t="s">
@@ -8057,13 +8057,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="88"/>
+      <c r="A222" s="81"/>
       <c r="B222" s="52" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="86" t="s">
+      <c r="A223" s="79" t="s">
         <v>282</v>
       </c>
       <c r="B223" s="49" t="s">
@@ -8071,31 +8071,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="87"/>
+      <c r="A224" s="80"/>
       <c r="B224" s="50" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="87"/>
+      <c r="A225" s="80"/>
       <c r="B225" s="50" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="87"/>
+      <c r="A226" s="80"/>
       <c r="B226" s="50" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="88"/>
+      <c r="A227" s="81"/>
       <c r="B227" s="52" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="86" t="s">
+      <c r="A228" s="79" t="s">
         <v>288</v>
       </c>
       <c r="B228" s="49" t="s">
@@ -8103,31 +8103,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="87"/>
+      <c r="A229" s="80"/>
       <c r="B229" s="50" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="87"/>
+      <c r="A230" s="80"/>
       <c r="B230" s="50" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="87"/>
+      <c r="A231" s="80"/>
       <c r="B231" s="50" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="87"/>
+      <c r="A232" s="80"/>
       <c r="B232" s="50" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="88"/>
+      <c r="A233" s="81"/>
       <c r="B233" s="52" t="s">
         <v>294</v>
       </c>
@@ -8141,16 +8141,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="81" t="s">
+      <c r="A236" s="99" t="s">
         <v>297</v>
       </c>
-      <c r="B236" s="80"/>
+      <c r="B236" s="98"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="79" t="s">
+      <c r="A239" s="97" t="s">
         <v>298</v>
       </c>
-      <c r="B239" s="80"/>
+      <c r="B239" s="98"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="47"/>
@@ -8249,10 +8249,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="82" t="s">
+      <c r="A257" s="100" t="s">
         <v>315</v>
       </c>
-      <c r="B257" s="83"/>
+      <c r="B257" s="101"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="47"/>
@@ -8429,10 +8429,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="89" t="s">
+      <c r="A288" s="86" t="s">
         <v>345</v>
       </c>
-      <c r="B288" s="90"/>
+      <c r="B288" s="87"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="55"/>
@@ -8621,16 +8621,23 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="40">
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A236:B236"/>
+    <mergeCell ref="A239:B239"/>
+    <mergeCell ref="A257:B257"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A139:A143"/>
+    <mergeCell ref="A144:A150"/>
+    <mergeCell ref="A151:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="A191:A198"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A201:A203"/>
+    <mergeCell ref="A204:A207"/>
     <mergeCell ref="A288:B288"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -8647,22 +8654,14 @@
     <mergeCell ref="A72:A88"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="A239:B239"/>
-    <mergeCell ref="A257:B257"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A139:A143"/>
-    <mergeCell ref="A144:A150"/>
-    <mergeCell ref="A151:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A198"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A203"/>
-    <mergeCell ref="A204:A207"/>
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8682,10 +8681,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="111" t="s">
         <v>377</v>
       </c>
-      <c r="B1" s="103"/>
+      <c r="B1" s="112"/>
     </row>
     <row r="2" spans="1:2" s="15" customFormat="1" ht="14.25">
       <c r="A2" s="18" t="s">
@@ -8699,7 +8698,7 @@
       <c r="A3" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="105" t="s">
         <v>1</v>
       </c>
     </row>
@@ -8707,25 +8706,25 @@
       <c r="A4" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="B4" s="105"/>
+      <c r="B4" s="106"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="105"/>
+      <c r="B5" s="106"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="106"/>
+      <c r="B6" s="107"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="105" t="s">
         <v>382</v>
       </c>
     </row>
@@ -8733,25 +8732,25 @@
       <c r="A8" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="105"/>
+      <c r="B8" s="106"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="105"/>
+      <c r="B9" s="106"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="106"/>
+      <c r="B10" s="107"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="104" t="s">
+      <c r="B11" s="105" t="s">
         <v>2</v>
       </c>
     </row>
@@ -8759,85 +8758,85 @@
       <c r="A12" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="105"/>
+      <c r="B12" s="106"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="105"/>
+      <c r="B13" s="106"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="105"/>
+      <c r="B14" s="106"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="105"/>
+      <c r="B15" s="106"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="105"/>
+      <c r="B16" s="106"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="105"/>
+      <c r="B17" s="106"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="B18" s="105"/>
+      <c r="B18" s="106"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="105"/>
+      <c r="B19" s="106"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="21" t="s">
         <v>384</v>
       </c>
-      <c r="B20" s="105"/>
+      <c r="B20" s="106"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="26" t="s">
         <v>385</v>
       </c>
-      <c r="B21" s="105"/>
+      <c r="B21" s="106"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="105"/>
+      <c r="B22" s="106"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="107"/>
+      <c r="B23" s="113"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="108"/>
+      <c r="B24" s="114"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="B25" s="104" t="s">
+      <c r="B25" s="105" t="s">
         <v>3</v>
       </c>
     </row>
@@ -8845,61 +8844,61 @@
       <c r="A26" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="105"/>
+      <c r="B26" s="106"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="105"/>
+      <c r="B27" s="106"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="105"/>
+      <c r="B28" s="106"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="105"/>
+      <c r="B29" s="106"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="B30" s="105"/>
+      <c r="B30" s="106"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="105"/>
+      <c r="B31" s="106"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="B32" s="105"/>
+      <c r="B32" s="106"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="21" t="s">
         <v>389</v>
       </c>
-      <c r="B33" s="105"/>
+      <c r="B33" s="106"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="106"/>
+      <c r="B34" s="107"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="29" t="s">
         <v>390</v>
       </c>
-      <c r="B35" s="104" t="s">
+      <c r="B35" s="105" t="s">
         <v>391</v>
       </c>
     </row>
@@ -8907,13 +8906,13 @@
       <c r="A36" s="28" t="s">
         <v>392</v>
       </c>
-      <c r="B36" s="106"/>
+      <c r="B36" s="107"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="104" t="s">
+      <c r="B37" s="105" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8921,19 +8920,19 @@
       <c r="A38" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="105"/>
+      <c r="B38" s="106"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="105"/>
+      <c r="B39" s="106"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="B40" s="104" t="s">
+      <c r="B40" s="105" t="s">
         <v>394</v>
       </c>
     </row>
@@ -8941,37 +8940,37 @@
       <c r="A41" s="21" t="s">
         <v>395</v>
       </c>
-      <c r="B41" s="105"/>
+      <c r="B41" s="106"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="105"/>
+      <c r="B42" s="106"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="B43" s="105"/>
+      <c r="B43" s="106"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="21" t="s">
         <v>397</v>
       </c>
-      <c r="B44" s="105"/>
+      <c r="B44" s="106"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="B45" s="105"/>
+      <c r="B45" s="106"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="106"/>
+      <c r="B46" s="107"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="30" t="s">
@@ -8985,7 +8984,7 @@
       <c r="A48" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="104" t="s">
+      <c r="B48" s="105" t="s">
         <v>398</v>
       </c>
     </row>
@@ -8993,13 +8992,13 @@
       <c r="A49" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B49" s="106"/>
+      <c r="B49" s="107"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B50" s="104" t="s">
+      <c r="B50" s="105" t="s">
         <v>6</v>
       </c>
     </row>
@@ -9007,25 +9006,25 @@
       <c r="A51" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B51" s="105"/>
+      <c r="B51" s="106"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="105"/>
+      <c r="B52" s="106"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="B53" s="105"/>
+      <c r="B53" s="106"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="106"/>
+      <c r="B54" s="107"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="30" t="s">
@@ -9039,7 +9038,7 @@
       <c r="A56" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="104" t="s">
+      <c r="B56" s="105" t="s">
         <v>8</v>
       </c>
     </row>
@@ -9047,19 +9046,19 @@
       <c r="A57" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B57" s="105"/>
+      <c r="B57" s="106"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B58" s="106"/>
+      <c r="B58" s="107"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="B59" s="104" t="s">
+      <c r="B59" s="105" t="s">
         <v>7</v>
       </c>
     </row>
@@ -9067,37 +9066,37 @@
       <c r="A60" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="105"/>
+      <c r="B60" s="106"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="B61" s="105"/>
+      <c r="B61" s="106"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B62" s="105"/>
+      <c r="B62" s="106"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="B63" s="105"/>
+      <c r="B63" s="106"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="B64" s="106"/>
+      <c r="B64" s="107"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="21" t="s">
         <v>401</v>
       </c>
-      <c r="B65" s="112" t="s">
+      <c r="B65" s="108" t="s">
         <v>402</v>
       </c>
     </row>
@@ -9105,26 +9104,26 @@
       <c r="A66" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B66" s="113"/>
+      <c r="B66" s="109"/>
       <c r="E66" s="33"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B67" s="113"/>
+      <c r="B67" s="109"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="21" t="s">
         <v>403</v>
       </c>
-      <c r="B68" s="114"/>
+      <c r="B68" s="110"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="B69" s="104" t="s">
+      <c r="B69" s="105" t="s">
         <v>9</v>
       </c>
     </row>
@@ -9132,37 +9131,37 @@
       <c r="A70" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B70" s="105"/>
+      <c r="B70" s="106"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="B71" s="105"/>
+      <c r="B71" s="106"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="B72" s="105"/>
+      <c r="B72" s="106"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="B73" s="105"/>
+      <c r="B73" s="106"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="B74" s="106"/>
+      <c r="B74" s="107"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="B75" s="104" t="s">
+      <c r="B75" s="105" t="s">
         <v>10</v>
       </c>
     </row>
@@ -9170,139 +9169,139 @@
       <c r="A76" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="B76" s="105"/>
+      <c r="B76" s="106"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="B77" s="105"/>
+      <c r="B77" s="106"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="B78" s="105"/>
+      <c r="B78" s="106"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="B79" s="105"/>
+      <c r="B79" s="106"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="B80" s="105"/>
+      <c r="B80" s="106"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="B81" s="105"/>
+      <c r="B81" s="106"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="B82" s="105"/>
+      <c r="B82" s="106"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B83" s="105"/>
+      <c r="B83" s="106"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="B84" s="105"/>
+      <c r="B84" s="106"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="B85" s="105"/>
+      <c r="B85" s="106"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="B86" s="105"/>
+      <c r="B86" s="106"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B87" s="105"/>
+      <c r="B87" s="106"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="B88" s="105"/>
+      <c r="B88" s="106"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="B89" s="105"/>
+      <c r="B89" s="106"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="B90" s="105"/>
+      <c r="B90" s="106"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="B91" s="105"/>
+      <c r="B91" s="106"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="B92" s="105"/>
+      <c r="B92" s="106"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="B93" s="105"/>
+      <c r="B93" s="106"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="B94" s="105"/>
+      <c r="B94" s="106"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="B95" s="105"/>
+      <c r="B95" s="106"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="B96" s="105"/>
+      <c r="B96" s="106"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="B97" s="105"/>
+      <c r="B97" s="106"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="B98" s="109" t="s">
+      <c r="B98" s="102" t="s">
         <v>11</v>
       </c>
     </row>
@@ -9310,37 +9309,37 @@
       <c r="A99" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="B99" s="110"/>
+      <c r="B99" s="103"/>
     </row>
     <row r="100" spans="1:2" s="16" customFormat="1">
       <c r="A100" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="B100" s="110"/>
+      <c r="B100" s="103"/>
     </row>
     <row r="101" spans="1:2" s="16" customFormat="1">
       <c r="A101" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="B101" s="110"/>
+      <c r="B101" s="103"/>
     </row>
     <row r="102" spans="1:2" s="16" customFormat="1">
       <c r="A102" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="B102" s="110"/>
+      <c r="B102" s="103"/>
     </row>
     <row r="103" spans="1:2" s="16" customFormat="1">
       <c r="A103" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="B103" s="110"/>
+      <c r="B103" s="103"/>
     </row>
     <row r="104" spans="1:2" s="16" customFormat="1">
       <c r="A104" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="B104" s="111"/>
+      <c r="B104" s="104"/>
     </row>
     <row r="105" spans="1:2" s="16" customFormat="1">
       <c r="A105" s="38" t="s">
@@ -9352,22 +9351,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepFinanciallInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepFinanciallInfo.xlsx
@@ -2649,9 +2649,6 @@
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">金融衍生品 </t>
-  </si>
-  <si>
     <t>*名称</t>
   </si>
   <si>
@@ -3916,6 +3913,10 @@
   </si>
   <si>
     <t>ZWE 津巴布韦</t>
+  </si>
+  <si>
+    <t>金融衍生品</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4595,27 +4596,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4623,6 +4603,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4649,40 +4641,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4695,6 +4675,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4702,6 +4691,18 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5080,7 +5081,7 @@
       <c r="D1" s="63"/>
       <c r="E1" s="64"/>
       <c r="F1" s="66" t="s">
-        <v>491</v>
+        <v>913</v>
       </c>
       <c r="G1" s="67"/>
       <c r="H1" s="67"/>
@@ -5110,22 +5111,22 @@
         <v>17</v>
       </c>
       <c r="F2" s="60" t="s">
+        <v>491</v>
+      </c>
+      <c r="G2" s="60" t="s">
         <v>492</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="H2" s="60" t="s">
         <v>493</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="I2" s="60" t="s">
         <v>494</v>
-      </c>
-      <c r="I2" s="60" t="s">
-        <v>495</v>
       </c>
       <c r="J2" s="55" t="s">
         <v>18</v>
       </c>
       <c r="K2" s="54" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L2" s="56" t="s">
         <v>19</v>
@@ -5279,13 +5280,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="69"/>
+      <c r="B1" s="87"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="77" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="18" t="s">
@@ -5293,25 +5294,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="81"/>
+      <c r="A3" s="78"/>
       <c r="B3" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="81"/>
+      <c r="A4" s="78"/>
       <c r="B4" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="82"/>
+      <c r="A5" s="79"/>
       <c r="B5" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="6" customFormat="1">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="80" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -5319,13 +5320,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="6" customFormat="1">
-      <c r="A7" s="84"/>
+      <c r="A7" s="81"/>
       <c r="B7" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="6" customFormat="1">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="82" t="s">
         <v>38</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -5333,13 +5334,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="6" customFormat="1">
-      <c r="A9" s="84"/>
+      <c r="A9" s="81"/>
       <c r="B9" s="12" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="83" t="s">
         <v>41</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5347,61 +5348,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="86"/>
+      <c r="A11" s="84"/>
       <c r="B11" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="86"/>
+      <c r="A12" s="84"/>
       <c r="B12" s="15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="86"/>
+      <c r="A13" s="84"/>
       <c r="B13" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="86"/>
+      <c r="A14" s="84"/>
       <c r="B14" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="86"/>
+      <c r="A15" s="84"/>
       <c r="B15" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="86"/>
+      <c r="A16" s="84"/>
       <c r="B16" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="86"/>
+      <c r="A17" s="84"/>
       <c r="B17" s="15" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="86"/>
+      <c r="A18" s="84"/>
       <c r="B18" s="15" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="86"/>
+      <c r="A19" s="84"/>
       <c r="B19" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="86"/>
+      <c r="A20" s="84"/>
       <c r="B20" s="15" t="s">
         <v>52</v>
       </c>
@@ -5415,7 +5416,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="73" t="s">
+      <c r="A22" s="83" t="s">
         <v>55</v>
       </c>
       <c r="B22" s="18" t="s">
@@ -5423,19 +5424,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="86"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="15" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="74"/>
+      <c r="A24" s="85"/>
       <c r="B24" s="13" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="73" t="s">
+      <c r="A25" s="83" t="s">
         <v>59</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -5443,67 +5444,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="86"/>
+      <c r="A26" s="84"/>
       <c r="B26" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="86"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="10" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="86"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="10" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="86"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="10" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="86"/>
+      <c r="A30" s="84"/>
       <c r="B30" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="86"/>
+      <c r="A31" s="84"/>
       <c r="B31" s="10" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="86"/>
+      <c r="A32" s="84"/>
       <c r="B32" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="86"/>
+      <c r="A33" s="84"/>
       <c r="B33" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="86"/>
+      <c r="A34" s="84"/>
       <c r="B34" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="74"/>
+      <c r="A35" s="85"/>
       <c r="B35" s="30" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="73" t="s">
+      <c r="A36" s="83" t="s">
         <v>71</v>
       </c>
       <c r="B36" s="10" t="s">
@@ -5511,25 +5512,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="86"/>
+      <c r="A37" s="84"/>
       <c r="B37" s="15" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="86"/>
+      <c r="A38" s="84"/>
       <c r="B38" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="74"/>
+      <c r="A39" s="85"/>
       <c r="B39" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="73" t="s">
+      <c r="A40" s="83" t="s">
         <v>76</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -5537,43 +5538,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="86"/>
+      <c r="A41" s="84"/>
       <c r="B41" s="10" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="86"/>
+      <c r="A42" s="84"/>
       <c r="B42" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="86"/>
+      <c r="A43" s="84"/>
       <c r="B43" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="86"/>
+      <c r="A44" s="84"/>
       <c r="B44" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="86"/>
+      <c r="A45" s="84"/>
       <c r="B45" s="10" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="74"/>
+      <c r="A46" s="85"/>
       <c r="B46" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="73" t="s">
+      <c r="A47" s="83" t="s">
         <v>84</v>
       </c>
       <c r="B47" s="18" t="s">
@@ -5581,61 +5582,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="86"/>
+      <c r="A48" s="84"/>
       <c r="B48" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="86"/>
+      <c r="A49" s="84"/>
       <c r="B49" s="10" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="86"/>
+      <c r="A50" s="84"/>
       <c r="B50" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="86"/>
+      <c r="A51" s="84"/>
       <c r="B51" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="86"/>
+      <c r="A52" s="84"/>
       <c r="B52" s="10" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="86"/>
+      <c r="A53" s="84"/>
       <c r="B53" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="86"/>
+      <c r="A54" s="84"/>
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="86"/>
+      <c r="A55" s="84"/>
       <c r="B55" s="15" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="74"/>
+      <c r="A56" s="85"/>
       <c r="B56" s="13" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="73" t="s">
+      <c r="A57" s="83" t="s">
         <v>95</v>
       </c>
       <c r="B57" s="9" t="s">
@@ -5643,19 +5644,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="86"/>
+      <c r="A58" s="84"/>
       <c r="B58" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="74"/>
+      <c r="A59" s="85"/>
       <c r="B59" s="13" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="73" t="s">
+      <c r="A60" s="83" t="s">
         <v>99</v>
       </c>
       <c r="B60" s="23" t="s">
@@ -5663,37 +5664,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="86"/>
+      <c r="A61" s="84"/>
       <c r="B61" s="10" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="86"/>
+      <c r="A62" s="84"/>
       <c r="B62" s="24" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="86"/>
+      <c r="A63" s="84"/>
       <c r="B63" s="10" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="86"/>
+      <c r="A64" s="84"/>
       <c r="B64" s="10" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="74"/>
+      <c r="A65" s="85"/>
       <c r="B65" s="17" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="73" t="s">
+      <c r="A66" s="83" t="s">
         <v>106</v>
       </c>
       <c r="B66" s="23" t="s">
@@ -5701,37 +5702,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="86"/>
+      <c r="A67" s="84"/>
       <c r="B67" s="10" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="86"/>
+      <c r="A68" s="84"/>
       <c r="B68" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="86"/>
+      <c r="A69" s="84"/>
       <c r="B69" s="10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="86"/>
+      <c r="A70" s="84"/>
       <c r="B70" s="10" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="74"/>
+      <c r="A71" s="85"/>
       <c r="B71" s="17" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="6" customFormat="1">
-      <c r="A72" s="73" t="s">
+      <c r="A72" s="83" t="s">
         <v>113</v>
       </c>
       <c r="B72" s="10" t="s">
@@ -5739,103 +5740,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="6" customFormat="1">
-      <c r="A73" s="86"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="10" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="6" customFormat="1">
-      <c r="A74" s="86"/>
+      <c r="A74" s="84"/>
       <c r="B74" s="10" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="6" customFormat="1">
-      <c r="A75" s="86"/>
+      <c r="A75" s="84"/>
       <c r="B75" s="10" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="6" customFormat="1">
-      <c r="A76" s="86"/>
+      <c r="A76" s="84"/>
       <c r="B76" s="10" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="6" customFormat="1">
-      <c r="A77" s="86"/>
+      <c r="A77" s="84"/>
       <c r="B77" s="25" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="6" customFormat="1">
-      <c r="A78" s="86"/>
+      <c r="A78" s="84"/>
       <c r="B78" s="10" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="6" customFormat="1">
-      <c r="A79" s="86"/>
+      <c r="A79" s="84"/>
       <c r="B79" s="10" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="6" customFormat="1">
-      <c r="A80" s="86"/>
+      <c r="A80" s="84"/>
       <c r="B80" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="6" customFormat="1">
-      <c r="A81" s="86"/>
+      <c r="A81" s="84"/>
       <c r="B81" s="25" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="6" customFormat="1">
-      <c r="A82" s="86"/>
+      <c r="A82" s="84"/>
       <c r="B82" s="10" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="6" customFormat="1">
-      <c r="A83" s="86"/>
+      <c r="A83" s="84"/>
       <c r="B83" s="10" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="6" customFormat="1">
-      <c r="A84" s="86"/>
+      <c r="A84" s="84"/>
       <c r="B84" s="10" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="6" customFormat="1">
-      <c r="A85" s="86"/>
+      <c r="A85" s="84"/>
       <c r="B85" s="25" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="6" customFormat="1">
-      <c r="A86" s="86"/>
+      <c r="A86" s="84"/>
       <c r="B86" s="25" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="6" customFormat="1">
-      <c r="A87" s="86"/>
+      <c r="A87" s="84"/>
       <c r="B87" s="25" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="6" customFormat="1">
-      <c r="A88" s="74"/>
+      <c r="A88" s="85"/>
       <c r="B88" s="13" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="6" customFormat="1">
-      <c r="A89" s="73" t="s">
+      <c r="A89" s="83" t="s">
         <v>131</v>
       </c>
       <c r="B89" s="15" t="s">
@@ -5843,38 +5844,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="6" customFormat="1">
-      <c r="A90" s="86"/>
+      <c r="A90" s="84"/>
       <c r="B90" s="15" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="6" customFormat="1">
-      <c r="A91" s="86"/>
+      <c r="A91" s="84"/>
       <c r="B91" s="15" t="s">
         <v>134</v>
       </c>
       <c r="F91" s="31"/>
     </row>
     <row r="92" spans="1:6" s="6" customFormat="1">
-      <c r="A92" s="86"/>
+      <c r="A92" s="84"/>
       <c r="B92" s="32" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="6" customFormat="1">
-      <c r="A93" s="86"/>
+      <c r="A93" s="84"/>
       <c r="B93" s="15" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="6" customFormat="1">
-      <c r="A94" s="74"/>
+      <c r="A94" s="85"/>
       <c r="B94" s="13" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="6" customFormat="1">
-      <c r="A95" s="73" t="s">
+      <c r="A95" s="83" t="s">
         <v>138</v>
       </c>
       <c r="B95" s="26" t="s">
@@ -5882,43 +5883,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="6" customFormat="1">
-      <c r="A96" s="86"/>
+      <c r="A96" s="84"/>
       <c r="B96" s="25" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="6" customFormat="1">
-      <c r="A97" s="86"/>
+      <c r="A97" s="84"/>
       <c r="B97" s="25" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="6" customFormat="1">
-      <c r="A98" s="86"/>
+      <c r="A98" s="84"/>
       <c r="B98" s="25" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="6" customFormat="1">
-      <c r="A99" s="86"/>
+      <c r="A99" s="84"/>
       <c r="B99" s="25" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="6" customFormat="1">
-      <c r="A100" s="86"/>
+      <c r="A100" s="84"/>
       <c r="B100" s="25" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="6" customFormat="1">
-      <c r="A101" s="74"/>
+      <c r="A101" s="85"/>
       <c r="B101" s="21" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="6" customFormat="1">
-      <c r="A102" s="73" t="s">
+      <c r="A102" s="83" t="s">
         <v>146</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -5926,7 +5927,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="6" customFormat="1">
-      <c r="A103" s="74"/>
+      <c r="A103" s="85"/>
       <c r="B103" s="13" t="s">
         <v>148</v>
       </c>
@@ -5944,10 +5945,10 @@
       <c r="B105" s="16"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="68" t="s">
+      <c r="A107" s="86" t="s">
         <v>151</v>
       </c>
-      <c r="B107" s="69"/>
+      <c r="B107" s="87"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="36"/>
@@ -6118,17 +6119,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="87" t="s">
+      <c r="A137" s="71" t="s">
         <v>180</v>
       </c>
-      <c r="B137" s="88"/>
+      <c r="B137" s="72"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="89"/>
-      <c r="B138" s="90"/>
+      <c r="A138" s="73"/>
+      <c r="B138" s="74"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="75" t="s">
+      <c r="A139" s="68" t="s">
         <v>181</v>
       </c>
       <c r="B139" s="38" t="s">
@@ -6136,31 +6137,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="76"/>
+      <c r="A140" s="69"/>
       <c r="B140" s="39" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="76"/>
+      <c r="A141" s="69"/>
       <c r="B141" s="39" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="76"/>
+      <c r="A142" s="69"/>
       <c r="B142" s="39" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="77"/>
+      <c r="A143" s="70"/>
       <c r="B143" s="41" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="75" t="s">
+      <c r="A144" s="68" t="s">
         <v>187</v>
       </c>
       <c r="B144" s="38" t="s">
@@ -6168,43 +6169,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="76"/>
+      <c r="A145" s="69"/>
       <c r="B145" s="39" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="76"/>
+      <c r="A146" s="69"/>
       <c r="B146" s="39" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="76"/>
+      <c r="A147" s="69"/>
       <c r="B147" s="39" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="76"/>
+      <c r="A148" s="69"/>
       <c r="B148" s="39" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="76"/>
+      <c r="A149" s="69"/>
       <c r="B149" s="39" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="77"/>
+      <c r="A150" s="70"/>
       <c r="B150" s="41" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="75" t="s">
+      <c r="A151" s="68" t="s">
         <v>195</v>
       </c>
       <c r="B151" s="38" t="s">
@@ -6212,187 +6213,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="76"/>
+      <c r="A152" s="69"/>
       <c r="B152" s="39" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="76"/>
+      <c r="A153" s="69"/>
       <c r="B153" s="39" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="76"/>
+      <c r="A154" s="69"/>
       <c r="B154" s="39" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="76"/>
+      <c r="A155" s="69"/>
       <c r="B155" s="39" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="76"/>
+      <c r="A156" s="69"/>
       <c r="B156" s="39" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="76"/>
+      <c r="A157" s="69"/>
       <c r="B157" s="39" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="76"/>
+      <c r="A158" s="69"/>
       <c r="B158" s="39" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="76"/>
+      <c r="A159" s="69"/>
       <c r="B159" s="39" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="76"/>
+      <c r="A160" s="69"/>
       <c r="B160" s="39" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="76"/>
+      <c r="A161" s="69"/>
       <c r="B161" s="39" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="76"/>
+      <c r="A162" s="69"/>
       <c r="B162" s="39" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="76"/>
+      <c r="A163" s="69"/>
       <c r="B163" s="39" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="76"/>
+      <c r="A164" s="69"/>
       <c r="B164" s="39" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="76"/>
+      <c r="A165" s="69"/>
       <c r="B165" s="39" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="76"/>
+      <c r="A166" s="69"/>
       <c r="B166" s="39" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="76"/>
+      <c r="A167" s="69"/>
       <c r="B167" s="39" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="76"/>
+      <c r="A168" s="69"/>
       <c r="B168" s="39" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="76"/>
+      <c r="A169" s="69"/>
       <c r="B169" s="39" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="76"/>
+      <c r="A170" s="69"/>
       <c r="B170" s="39" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="76"/>
+      <c r="A171" s="69"/>
       <c r="B171" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="76"/>
+      <c r="A172" s="69"/>
       <c r="B172" s="39" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="76"/>
+      <c r="A173" s="69"/>
       <c r="B173" s="39" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="76"/>
+      <c r="A174" s="69"/>
       <c r="B174" s="39" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="76"/>
+      <c r="A175" s="69"/>
       <c r="B175" s="39" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="76"/>
+      <c r="A176" s="69"/>
       <c r="B176" s="39" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="76"/>
+      <c r="A177" s="69"/>
       <c r="B177" s="39" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="76"/>
+      <c r="A178" s="69"/>
       <c r="B178" s="39" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="76"/>
+      <c r="A179" s="69"/>
       <c r="B179" s="39" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="76"/>
+      <c r="A180" s="69"/>
       <c r="B180" s="39" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="77"/>
+      <c r="A181" s="70"/>
       <c r="B181" s="41" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="75" t="s">
+      <c r="A182" s="68" t="s">
         <v>227</v>
       </c>
       <c r="B182" s="38" t="s">
@@ -6400,19 +6401,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="76"/>
+      <c r="A183" s="69"/>
       <c r="B183" s="39" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="77"/>
+      <c r="A184" s="70"/>
       <c r="B184" s="41" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="75" t="s">
+      <c r="A185" s="68" t="s">
         <v>231</v>
       </c>
       <c r="B185" s="38" t="s">
@@ -6420,25 +6421,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="76"/>
+      <c r="A186" s="69"/>
       <c r="B186" s="39" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="76"/>
+      <c r="A187" s="69"/>
       <c r="B187" s="39" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="77"/>
+      <c r="A188" s="70"/>
       <c r="B188" s="41" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="75" t="s">
+      <c r="A189" s="68" t="s">
         <v>236</v>
       </c>
       <c r="B189" s="38" t="s">
@@ -6446,13 +6447,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="77"/>
+      <c r="A190" s="70"/>
       <c r="B190" s="41" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="75" t="s">
+      <c r="A191" s="68" t="s">
         <v>239</v>
       </c>
       <c r="B191" s="38" t="s">
@@ -6460,49 +6461,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="76"/>
+      <c r="A192" s="69"/>
       <c r="B192" s="39" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="76"/>
+      <c r="A193" s="69"/>
       <c r="B193" s="39" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="76"/>
+      <c r="A194" s="69"/>
       <c r="B194" s="39" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="76"/>
+      <c r="A195" s="69"/>
       <c r="B195" s="39" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="76"/>
+      <c r="A196" s="69"/>
       <c r="B196" s="39" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="76"/>
+      <c r="A197" s="69"/>
       <c r="B197" s="39" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="77"/>
+      <c r="A198" s="70"/>
       <c r="B198" s="41" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="75" t="s">
+      <c r="A199" s="68" t="s">
         <v>248</v>
       </c>
       <c r="B199" s="38" t="s">
@@ -6510,13 +6511,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="77"/>
+      <c r="A200" s="70"/>
       <c r="B200" s="41" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="75" t="s">
+      <c r="A201" s="68" t="s">
         <v>251</v>
       </c>
       <c r="B201" s="38" t="s">
@@ -6524,19 +6525,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="76"/>
+      <c r="A202" s="69"/>
       <c r="B202" s="39" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="77"/>
+      <c r="A203" s="70"/>
       <c r="B203" s="41" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="75" t="s">
+      <c r="A204" s="68" t="s">
         <v>255</v>
       </c>
       <c r="B204" s="38" t="s">
@@ -6544,19 +6545,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="76"/>
+      <c r="A205" s="69"/>
       <c r="B205" s="39" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="76"/>
+      <c r="A206" s="69"/>
       <c r="B206" s="39" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="77"/>
+      <c r="A207" s="70"/>
       <c r="B207" s="41" t="s">
         <v>259</v>
       </c>
@@ -6570,7 +6571,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="75" t="s">
+      <c r="A209" s="68" t="s">
         <v>262</v>
       </c>
       <c r="B209" s="38" t="s">
@@ -6578,13 +6579,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="77"/>
+      <c r="A210" s="70"/>
       <c r="B210" s="41" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="75" t="s">
+      <c r="A211" s="68" t="s">
         <v>265</v>
       </c>
       <c r="B211" s="38" t="s">
@@ -6592,19 +6593,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="76"/>
+      <c r="A212" s="69"/>
       <c r="B212" s="39" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="77"/>
+      <c r="A213" s="70"/>
       <c r="B213" s="41" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="75" t="s">
+      <c r="A214" s="68" t="s">
         <v>269</v>
       </c>
       <c r="B214" s="38" t="s">
@@ -6612,19 +6613,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="76"/>
+      <c r="A215" s="69"/>
       <c r="B215" s="39" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="77"/>
+      <c r="A216" s="70"/>
       <c r="B216" s="41" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="75" t="s">
+      <c r="A217" s="68" t="s">
         <v>273</v>
       </c>
       <c r="B217" s="38" t="s">
@@ -6632,13 +6633,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="76"/>
+      <c r="A218" s="69"/>
       <c r="B218" s="39" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="77"/>
+      <c r="A219" s="70"/>
       <c r="B219" s="41" t="s">
         <v>276</v>
       </c>
@@ -6652,7 +6653,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="75" t="s">
+      <c r="A221" s="68" t="s">
         <v>279</v>
       </c>
       <c r="B221" s="38" t="s">
@@ -6660,13 +6661,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="77"/>
+      <c r="A222" s="70"/>
       <c r="B222" s="41" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="75" t="s">
+      <c r="A223" s="68" t="s">
         <v>282</v>
       </c>
       <c r="B223" s="38" t="s">
@@ -6674,31 +6675,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="76"/>
+      <c r="A224" s="69"/>
       <c r="B224" s="39" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="76"/>
+      <c r="A225" s="69"/>
       <c r="B225" s="39" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="76"/>
+      <c r="A226" s="69"/>
       <c r="B226" s="39" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="77"/>
+      <c r="A227" s="70"/>
       <c r="B227" s="41" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="75" t="s">
+      <c r="A228" s="68" t="s">
         <v>288</v>
       </c>
       <c r="B228" s="38" t="s">
@@ -6706,31 +6707,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="76"/>
+      <c r="A229" s="69"/>
       <c r="B229" s="39" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="76"/>
+      <c r="A230" s="69"/>
       <c r="B230" s="39" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="76"/>
+      <c r="A231" s="69"/>
       <c r="B231" s="39" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="76"/>
+      <c r="A232" s="69"/>
       <c r="B232" s="39" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="77"/>
+      <c r="A233" s="70"/>
       <c r="B233" s="41" t="s">
         <v>294</v>
       </c>
@@ -6744,16 +6745,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="70" t="s">
+      <c r="A236" s="88" t="s">
         <v>297</v>
       </c>
-      <c r="B236" s="69"/>
+      <c r="B236" s="87"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="68" t="s">
+      <c r="A239" s="86" t="s">
         <v>298</v>
       </c>
-      <c r="B239" s="69"/>
+      <c r="B239" s="87"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="36"/>
@@ -6852,10 +6853,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="71" t="s">
+      <c r="A257" s="89" t="s">
         <v>315</v>
       </c>
-      <c r="B257" s="72"/>
+      <c r="B257" s="90"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="36"/>
@@ -7032,10 +7033,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="78" t="s">
+      <c r="A288" s="75" t="s">
         <v>345</v>
       </c>
-      <c r="B288" s="79"/>
+      <c r="B288" s="76"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="44"/>
@@ -7225,14 +7226,22 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A236:B236"/>
+    <mergeCell ref="A239:B239"/>
+    <mergeCell ref="A257:B257"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A139:A143"/>
+    <mergeCell ref="A144:A150"/>
+    <mergeCell ref="A151:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="A191:A198"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A201:A203"/>
+    <mergeCell ref="A204:A207"/>
     <mergeCell ref="A288:B288"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -7249,22 +7258,14 @@
     <mergeCell ref="A72:A88"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="A239:B239"/>
-    <mergeCell ref="A257:B257"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A139:A143"/>
-    <mergeCell ref="A144:A150"/>
-    <mergeCell ref="A151:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A198"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A203"/>
-    <mergeCell ref="A204:A207"/>
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7284,10 +7285,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="100" t="s">
         <v>377</v>
       </c>
-      <c r="B1" s="92"/>
+      <c r="B1" s="101"/>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" ht="14.25">
       <c r="A2" s="7" t="s">
@@ -7301,7 +7302,7 @@
       <c r="A3" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="B3" s="93" t="s">
+      <c r="B3" s="94" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7309,25 +7310,25 @@
       <c r="A4" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="B4" s="94"/>
+      <c r="B4" s="95"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="94"/>
+      <c r="B5" s="95"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="95"/>
+      <c r="B6" s="96"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="93" t="s">
+      <c r="B7" s="94" t="s">
         <v>382</v>
       </c>
     </row>
@@ -7335,25 +7336,25 @@
       <c r="A8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="94"/>
+      <c r="B8" s="95"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="94"/>
+      <c r="B9" s="95"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="95"/>
+      <c r="B10" s="96"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="93" t="s">
+      <c r="B11" s="94" t="s">
         <v>2</v>
       </c>
     </row>
@@ -7361,85 +7362,85 @@
       <c r="A12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="94"/>
+      <c r="B12" s="95"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="94"/>
+      <c r="B13" s="95"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="94"/>
+      <c r="B14" s="95"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="94"/>
+      <c r="B15" s="95"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="94"/>
+      <c r="B16" s="95"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="94"/>
+      <c r="B17" s="95"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="B18" s="94"/>
+      <c r="B18" s="95"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="94"/>
+      <c r="B19" s="95"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B20" s="94"/>
+      <c r="B20" s="95"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="B21" s="94"/>
+      <c r="B21" s="95"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="94"/>
+      <c r="B22" s="95"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="96"/>
+      <c r="B23" s="102"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="97"/>
+      <c r="B24" s="103"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="B25" s="93" t="s">
+      <c r="B25" s="94" t="s">
         <v>3</v>
       </c>
     </row>
@@ -7447,61 +7448,61 @@
       <c r="A26" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="94"/>
+      <c r="B26" s="95"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="94"/>
+      <c r="B27" s="95"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="94"/>
+      <c r="B28" s="95"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="94"/>
+      <c r="B29" s="95"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B30" s="94"/>
+      <c r="B30" s="95"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="94"/>
+      <c r="B31" s="95"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="B32" s="94"/>
+      <c r="B32" s="95"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="B33" s="94"/>
+      <c r="B33" s="95"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="95"/>
+      <c r="B34" s="96"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="B35" s="93" t="s">
+      <c r="B35" s="94" t="s">
         <v>391</v>
       </c>
     </row>
@@ -7509,13 +7510,13 @@
       <c r="A36" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="B36" s="95"/>
+      <c r="B36" s="96"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="93" t="s">
+      <c r="B37" s="94" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7523,19 +7524,19 @@
       <c r="A38" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="94"/>
+      <c r="B38" s="95"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="94"/>
+      <c r="B39" s="95"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="B40" s="93" t="s">
+      <c r="B40" s="94" t="s">
         <v>394</v>
       </c>
     </row>
@@ -7543,37 +7544,37 @@
       <c r="A41" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="B41" s="94"/>
+      <c r="B41" s="95"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="94"/>
+      <c r="B42" s="95"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B43" s="94"/>
+      <c r="B43" s="95"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B44" s="94"/>
+      <c r="B44" s="95"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B45" s="94"/>
+      <c r="B45" s="95"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="95"/>
+      <c r="B46" s="96"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="19" t="s">
@@ -7587,7 +7588,7 @@
       <c r="A48" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="93" t="s">
+      <c r="B48" s="94" t="s">
         <v>398</v>
       </c>
     </row>
@@ -7595,13 +7596,13 @@
       <c r="A49" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B49" s="95"/>
+      <c r="B49" s="96"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B50" s="93" t="s">
+      <c r="B50" s="94" t="s">
         <v>6</v>
       </c>
     </row>
@@ -7609,25 +7610,25 @@
       <c r="A51" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B51" s="94"/>
+      <c r="B51" s="95"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="94"/>
+      <c r="B52" s="95"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B53" s="94"/>
+      <c r="B53" s="95"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="95"/>
+      <c r="B54" s="96"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="19" t="s">
@@ -7641,7 +7642,7 @@
       <c r="A56" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="93" t="s">
+      <c r="B56" s="94" t="s">
         <v>8</v>
       </c>
     </row>
@@ -7649,19 +7650,19 @@
       <c r="A57" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B57" s="94"/>
+      <c r="B57" s="95"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B58" s="95"/>
+      <c r="B58" s="96"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B59" s="93" t="s">
+      <c r="B59" s="94" t="s">
         <v>7</v>
       </c>
     </row>
@@ -7669,37 +7670,37 @@
       <c r="A60" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="94"/>
+      <c r="B60" s="95"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B61" s="94"/>
+      <c r="B61" s="95"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B62" s="94"/>
+      <c r="B62" s="95"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B63" s="94"/>
+      <c r="B63" s="95"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B64" s="95"/>
+      <c r="B64" s="96"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="B65" s="101" t="s">
+      <c r="B65" s="97" t="s">
         <v>402</v>
       </c>
     </row>
@@ -7707,26 +7708,26 @@
       <c r="A66" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B66" s="102"/>
+      <c r="B66" s="98"/>
       <c r="E66" s="22"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B67" s="102"/>
+      <c r="B67" s="98"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="B68" s="103"/>
+      <c r="B68" s="99"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="B69" s="93" t="s">
+      <c r="B69" s="94" t="s">
         <v>9</v>
       </c>
     </row>
@@ -7734,37 +7735,37 @@
       <c r="A70" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B70" s="94"/>
+      <c r="B70" s="95"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B71" s="94"/>
+      <c r="B71" s="95"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B72" s="94"/>
+      <c r="B72" s="95"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B73" s="94"/>
+      <c r="B73" s="95"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B74" s="95"/>
+      <c r="B74" s="96"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B75" s="93" t="s">
+      <c r="B75" s="94" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7772,139 +7773,139 @@
       <c r="A76" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B76" s="94"/>
+      <c r="B76" s="95"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B77" s="94"/>
+      <c r="B77" s="95"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B78" s="94"/>
+      <c r="B78" s="95"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B79" s="94"/>
+      <c r="B79" s="95"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B80" s="94"/>
+      <c r="B80" s="95"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B81" s="94"/>
+      <c r="B81" s="95"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B82" s="94"/>
+      <c r="B82" s="95"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B83" s="94"/>
+      <c r="B83" s="95"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B84" s="94"/>
+      <c r="B84" s="95"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B85" s="94"/>
+      <c r="B85" s="95"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B86" s="94"/>
+      <c r="B86" s="95"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B87" s="94"/>
+      <c r="B87" s="95"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B88" s="94"/>
+      <c r="B88" s="95"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B89" s="94"/>
+      <c r="B89" s="95"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="B90" s="94"/>
+      <c r="B90" s="95"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B91" s="94"/>
+      <c r="B91" s="95"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B92" s="94"/>
+      <c r="B92" s="95"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B93" s="94"/>
+      <c r="B93" s="95"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="B94" s="94"/>
+      <c r="B94" s="95"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="B95" s="94"/>
+      <c r="B95" s="95"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="B96" s="94"/>
+      <c r="B96" s="95"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B97" s="94"/>
+      <c r="B97" s="95"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="B98" s="98" t="s">
+      <c r="B98" s="91" t="s">
         <v>11</v>
       </c>
     </row>
@@ -7912,37 +7913,37 @@
       <c r="A99" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="B99" s="99"/>
+      <c r="B99" s="92"/>
     </row>
     <row r="100" spans="1:2" s="5" customFormat="1">
       <c r="A100" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B100" s="99"/>
+      <c r="B100" s="92"/>
     </row>
     <row r="101" spans="1:2" s="5" customFormat="1">
       <c r="A101" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="B101" s="99"/>
+      <c r="B101" s="92"/>
     </row>
     <row r="102" spans="1:2" s="5" customFormat="1">
       <c r="A102" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B102" s="99"/>
+      <c r="B102" s="92"/>
     </row>
     <row r="103" spans="1:2" s="5" customFormat="1">
       <c r="A103" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B103" s="99"/>
+      <c r="B103" s="92"/>
     </row>
     <row r="104" spans="1:2" s="5" customFormat="1">
       <c r="A104" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B104" s="100"/>
+      <c r="B104" s="93"/>
     </row>
     <row r="105" spans="1:2" s="5" customFormat="1">
       <c r="A105" s="27" t="s">
@@ -7954,22 +7955,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
@@ -8012,1197 +8013,1197 @@
   <sheetData>
     <row r="1" spans="1:1" ht="27" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -9222,892 +9223,892 @@
   <sheetData>
     <row r="1" spans="1:1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
   </sheetData>
